--- a/daily_matches/job_matches_2026-08-03.xlsx
+++ b/daily_matches/job_matches_2026-08-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,245 +468,560 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Gen AI Solutions Engineer #122</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Premier Cloud</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, BigQuery</t>
+          <t>Data Scientist, RAG, S3, EC2, Glue, Athena, Redshift, Data Lake, Kinesis, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab60a70d02e50c50</t>
+          <t>https://www.indeed.com/viewjob?jk=3ec018f4b793bb53</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior MuleSoft Engineer</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Green Irony</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.2</v>
+        <v>24.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, R, Java</t>
+          <t>Data Scientist, RAG, S3, EC2, Glue, Athena, Redshift, Data Lake, Kinesis, Kubernetes</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0eac49545af0ad</t>
+          <t>https://www.indeed.com/viewjob?jk=6c5406e0a898c0b3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior MuleSoft Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Green Irony</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Apex, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>24.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, R, Java</t>
+          <t>Data Scientist, RAG, S3, EC2, Glue, Athena, Redshift, Data Lake, Kinesis, Kubernetes</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=323e4c2e667bc8d4</t>
+          <t>https://www.indeed.com/viewjob?jk=51afe960d8622afb</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CLERA</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>24.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, SQL, R</t>
+          <t>Data Scientist, RAG, S3, EC2, Glue, Athena, Redshift, Data Lake, Kinesis, Kubernetes</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=217f5fa2f9c7a6b8</t>
+          <t>https://www.indeed.com/viewjob?jk=b6bdbda24615b096</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SprintRay</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>24.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, AKS, CI/CD, Git, R, Java, Scala</t>
+          <t>Data Scientist, RAG, S3, EC2, Glue, Athena, Redshift, Data Lake, Kinesis, Kubernetes</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ff49181ee5dfeee</t>
+          <t>https://www.indeed.com/viewjob?jk=8a792597231fd045</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr .NET Full Stack/AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Agilewoven LLC</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>24.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, S3, Docker, Git, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, S3, EC2, Glue, Athena, Redshift, Data Lake, Kinesis, Kubernetes</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c4caba2e708a794</t>
+          <t>https://www.indeed.com/viewjob?jk=49b79f56ab220c49</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python, Databricks</t>
+          <t>AI Engineer Mentor (Part-Time)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>LearnWise Solutions Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a18f1d7c9d073182</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Emerging Tech Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Copilot, FAISS, Pinecone, Prompt Engineering, Docker, Kubernetes, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f50254df57de18c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Emerging Tech Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Copilot, FAISS, Pinecone, Prompt Engineering, Docker, Kubernetes, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f76b422550e56c52</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Backend Software Engineer Intern (TikTok- PGC-Digital Content Center) - 2027 Summer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, Docker, Kubernetes, Git, Kafka, MySQL, MongoDB, NoSQL, SQL</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df7f3bd6cb74fbdd</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Sr. Database Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Terraform, PostgreSQL, MySQL, MongoDB, Cassandra, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=669e23632e4f9ad7</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Research Triangle Park, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=17e0fcf9d6680636</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Git, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3eab4072c0b0822a</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer Graduate (Brand Ads) - 2027 Start (PhD)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c47cdd5fea1d5376</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>TEEMA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>10</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>RAG, Databricks, Kafka, MongoDB, NoSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Databricks, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c0ee0a48cf92aa8</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer Graduate (Ads Targeting)- 2027 Start</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Python, SQL, R, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>2026-08-02</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=291bce23f034d334</t>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c35f431f5471656a</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-03.xlsx
+++ b/daily_matches/job_matches_2026-08-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Edurech Technoogy</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Florida City, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.4</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, EC2, Glue, Athena, Redshift, Data Lake, Kinesis, Kubernetes</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Keras, MLflow, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ec018f4b793bb53</t>
+          <t>https://www.indeed.com/viewjob?jk=255fa6809083315d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Edurech Technoogy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Landers, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>24.4</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, EC2, Glue, Athena, Redshift, Data Lake, Kinesis, Kubernetes</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Keras, Hadoop, Tableau, Power BI, Matplotlib, Seaborn</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c5406e0a898c0b3</t>
+          <t>https://www.indeed.com/viewjob?jk=435b4faa1bb26f3c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Arktek Staffing Solutions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>24.4</v>
+        <v>12.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, EC2, Glue, Athena, Redshift, Data Lake, Kinesis, Kubernetes</t>
+          <t>Generative AI, RAG, Prompt Engineering, S3, EC2, Kubernetes, CI/CD, Terraform, PostgreSQL, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51afe960d8622afb</t>
+          <t>https://www.indeed.com/viewjob?jk=d2f7be1910dbeb10</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>2027 Data &amp; AI Program - Full Time - Analyst - United States</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>24.4</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, EC2, Glue, Athena, Redshift, Data Lake, Kinesis, Kubernetes</t>
+          <t>Data Scientist, RAG, Copilot, Prompt Engineering, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6bdbda24615b096</t>
+          <t>https://www.indeed.com/viewjob?jk=60250ef25bb6ecd2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>2027 Data &amp; AI Program - Summer Internship - Analyst - United States</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>24.4</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, EC2, Glue, Athena, Redshift, Data Lake, Kinesis, Kubernetes</t>
+          <t>Data Scientist, RAG, Copilot, Prompt Engineering, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a792597231fd045</t>
+          <t>https://www.indeed.com/viewjob?jk=7ab560f2d3f8978f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Platform Innovation and Engineering</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>24.4</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, EC2, Glue, Athena, Redshift, Data Lake, Kinesis, Kubernetes</t>
+          <t>RAG, Copilot, CI/CD, Git, Databricks, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b79f56ab220c49</t>
+          <t>https://www.indeed.com/viewjob?jk=0e28c74402fdf2d6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Engineer Mentor (Part-Time)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LearnWise Solutions Inc.</t>
+          <t>UDCYDE</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>21.1</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, MySQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a18f1d7c9d073182</t>
+          <t>https://www.indeed.com/viewjob?jk=7fd4e99dbd3da66e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Emerging Tech Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.6</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, FAISS, Pinecone, Prompt Engineering, Docker, Kubernetes, CI/CD, Git</t>
+          <t>S3, EC2, Jenkins, Git, Tableau, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f50254df57de18c5</t>
+          <t>https://www.indeed.com/viewjob?jk=e76b66fdbbfac5e0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Emerging Tech Engineer</t>
+          <t>2027 Data for Good Hackathon - Data &amp; AI Program - Summer Internship</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.6</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, FAISS, Pinecone, Prompt Engineering, Docker, Kubernetes, CI/CD, Git</t>
+          <t>RAG, Copilot, Prompt Engineering, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,252 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f76b422550e56c52</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Backend Software Engineer Intern (TikTok- PGC-Digital Content Center) - 2027 Summer</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>TikTok</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, Docker, Kubernetes, Git, Kafka, MySQL, MongoDB, NoSQL, SQL</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=df7f3bd6cb74fbdd</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Sr. Database Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Adobe</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Terraform, PostgreSQL, MySQL, MongoDB, Cassandra, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=669e23632e4f9ad7</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (Hybrid)</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Cisco</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Research Triangle Park, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=17e0fcf9d6680636</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, CI/CD, Git, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3eab4072c0b0822a</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer Graduate (Brand Ads) - 2027 Start (PhD)</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>TikTok</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c47cdd5fea1d5376</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Senior Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>TEEMA</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, Databricks, NoSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2c0ee0a48cf92aa8</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer Graduate (Ads Targeting)- 2027 Start</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>TikTok</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Python, SQL, R, Optimization, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c35f431f5471656a</t>
+          <t>https://www.indeed.com/viewjob?jk=d6a840599a311f8b</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-03.xlsx
+++ b/daily_matches/job_matches_2026-08-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Data Engineer With GenAI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Edurech Technoogy</t>
+          <t>Broadmind INC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Florida City, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Keras, MLflow, Docker, Kubernetes, CI/CD</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, ChromaDB</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=255fa6809083315d</t>
+          <t>https://www.indeed.com/viewjob?jk=2f790ceb1de06dfe</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Edurech Technoogy</t>
+          <t>TritonExec</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Landers, CA, US USA</t>
+          <t>Avenel, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Keras, Hadoop, Tableau, Power BI, Matplotlib, Seaborn</t>
+          <t>AI Engineer, Data Scientist, RAG, Cortex, Docker, Kubernetes, Apache Airflow, CI/CD, Git, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,19 +531,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=435b4faa1bb26f3c</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ea0da5bd509501</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AWS Platform Engineer</t>
+          <t>AI Engineer II ( AI Platform)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Arktek Staffing Solutions</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -552,11 +552,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, S3, EC2, Kubernetes, CI/CD, Terraform, PostgreSQL, SQL</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2f7be1910dbeb10</t>
+          <t>https://www.indeed.com/viewjob?jk=7fc8f75962758aae</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2027 Data &amp; AI Program - Full Time - Analyst - United States</t>
+          <t>Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>arrivia</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Prompt Engineering, Snowflake, Databricks, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Synapse, Dataflow, CI/CD, Git, Databricks, PySpark, Kafka, Power BI, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60250ef25bb6ecd2</t>
+          <t>https://www.indeed.com/viewjob?jk=99ee79c55904224f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2027 Data &amp; AI Program - Summer Internship - Analyst - United States</t>
+          <t>Engineer III - Software</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>PODS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Prompt Engineering, Snowflake, Databricks, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Snowflake, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab560f2d3f8978f</t>
+          <t>https://www.indeed.com/viewjob?jk=3cae15ef7a0cb0a0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer - Platform Innovation and Engineering</t>
+          <t>AI Engineer - Copilot Studio &amp; CCaaS (No visa sponsorship)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Antra, Inc</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, Databricks, Python, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e28c74402fdf2d6</t>
+          <t>https://www.indeed.com/viewjob?jk=087d64ff91b1f116</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Snowflake Data Platform Operations Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>UDCYDE</t>
+          <t>Stradit</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, MySQL, SQL, R, Java, Scala</t>
+          <t>Cortex, CI/CD, Jenkins, Terraform, Git, Snowflake, Power BI, Quicksight, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fd4e99dbd3da66e</t>
+          <t>https://www.indeed.com/viewjob?jk=b301884f870b69d9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Outfront Media</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Carlstadt, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>S3, EC2, Jenkins, Git, Tableau, Python, SQL, R, Java</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,42 +741,77 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e76b66fdbbfac5e0</t>
+          <t>https://www.indeed.com/viewjob?jk=aaaec41fa04316f0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2027 Data for Good Hackathon - Data &amp; AI Program - Summer Internship</t>
+          <t>Developer Advocate</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Teradata</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, Copilot, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5cc2b2e587d6e215</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>GRP Solutions</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Texas City, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>10</v>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Prompt Engineering, Snowflake, Databricks, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d6a840599a311f8b</t>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b06308b12190615</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-03.xlsx
+++ b/daily_matches/job_matches_2026-08-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer With GenAI</t>
+          <t>Senior Specialty Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Broadmind INC</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.3</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, ChromaDB</t>
+          <t>Generative AI, RAG, Copilot, BigQuery, FastAPI, Kubernetes, GitHub Actions, Terraform, Git, BigQuery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f790ceb1de06dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=3e1ab076bac74b1c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Applied AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TritonExec</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Avenel, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Cortex, Docker, Kubernetes, Apache Airflow, CI/CD, Git, Snowflake</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ea0da5bd509501</t>
+          <t>https://www.indeed.com/viewjob?jk=26738974b8469a72</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fc8f75962758aae</t>
+          <t>https://www.indeed.com/viewjob?jk=9ebcec5706e5970a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Fabric Data Engineer</t>
+          <t>Sr. Backend Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>arrivia</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Synapse, Dataflow, CI/CD, Git, Databricks, PySpark, Kafka, Power BI, Python</t>
+          <t>Generative AI, RAG, Copilot, Kubernetes, Terraform, Git, PostgreSQL, MySQL, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99ee79c55904224f</t>
+          <t>https://www.indeed.com/viewjob?jk=d8b19d5343bf31ae</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Engineer III - Software</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PODS</t>
+          <t>IPolarity LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Snowflake, PostgreSQL, SQL, R, Java</t>
+          <t>Data Scientist, AWS SageMaker, Azure ML, Kubernetes, CI/CD, Terraform, Git, Databricks, PySpark, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cae15ef7a0cb0a0</t>
+          <t>https://www.indeed.com/viewjob?jk=d5882bdc5a806f54</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Engineer - Copilot Studio &amp; CCaaS (No visa sponsorship)</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Antra, Inc</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=087d64ff91b1f116</t>
+          <t>https://www.indeed.com/viewjob?jk=a28196d6639ff9e7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Snowflake Data Platform Operations Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Stradit</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cortex, CI/CD, Jenkins, Terraform, Git, Snowflake, Power BI, Quicksight, Python, SQL</t>
+          <t>RAG, Docker, CI/CD, Git, PostgreSQL, MySQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b301884f870b69d9</t>
+          <t>https://www.indeed.com/viewjob?jk=b1f9392df8cc4ab5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Dev Ops Engineer</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Outfront Media</t>
+          <t>Progressive Technology Solutions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Carlstadt, NJ, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>Copilot, Docker, Kubernetes, AKS, CI/CD, Git, Kafka, SQL, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaaec41fa04316f0</t>
+          <t>https://www.indeed.com/viewjob?jk=c665fe23456b2833</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Developer Advocate</t>
+          <t>AWS + AI-Native Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Teradata</t>
+          <t>Senior Backend Developer</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Copilot, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>LangChain, RAG, LLaMA, Copilot, Pinecone, S3, EC2, MLflow, Git, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,42 +776,917 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc2b2e587d6e215</t>
+          <t>https://www.indeed.com/viewjob?jk=4a12625c776e70a7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer</t>
+          <t>Cloud-Native Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GRP Solutions</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=71f63292ca49d08f</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Autonomous Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Python, R</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c3fac1e6c2d2ae27</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Data Engineer, Palo Alto</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Rhombus Power</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, MySQL, MongoDB, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c52e39436d6debc6</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Engineer III - Software</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PODS</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Clearwater, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Snowflake, PostgreSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d77313a791b9bf92</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Sr Data Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>The Hershey Company</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Hershey, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, Databricks, PostgreSQL, MySQL, MongoDB, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21c0e185b38b0100</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>DevOps Engineer - Westlake, TX</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Westlake, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b75914a192898d1c</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>DevOps Engineer - Jersey City, NJ</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=09b326711b2a8ba0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Microsoft Azure Specialist</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=797c8733d467365d</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>DevOps Engineer - Merrimack, NH</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Merrimack, NH, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c9e5552345b9c43f</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Software Engineer - Storage Infrastructure (Senior+)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>COGENT SECURITY</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, S3, Athena, BigQuery, Terraform, Snowflake, Databricks, BigQuery, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd755b1e01cf4b25</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Software Engineer - Storage Infrastructure (Senior+)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>COGENT SECURITY</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, S3, Athena, BigQuery, Terraform, Snowflake, Databricks, BigQuery, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0249428e9fdabded</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (C++, Parser /Compiler Development)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Rocket Software</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Git, PostgreSQL, SQL, R, Java, C++, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=002ea5033c873dd5</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Software Engineer, Content APIs</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>NBCUniversal</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, MongoDB, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f1c8d538cec93de</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Saint Paul, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=29dcdada1d61a998</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Data Scientist - Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Cortland</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, Git, Databricks, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6c20e494fa3ce2a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Rhombus Power</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>10</v>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9b06308b12190615</t>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, MySQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec7f3e20ccb4fbba</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Founding AI Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, LLaMA, Copilot, Docker, Kubernetes, Python, R</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a641f290ec2d05d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>AI - Process Engineering - Advisor II</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Fiserv</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8f99bab2bfd7689</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Threat Detection &amp; Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Fiserv</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Berkeley Heights, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, CI/CD, Terraform, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21ba876d91e1bbc5</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer, AI Platform</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>EvenUp</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Kubernetes, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=683cede4bf7b562b</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Database and Applications Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Adams and Reese LLP</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>New Orleans, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Git, Power BI, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=345f590a256aabe4</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Software Engineer - Backend</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>COGENT SECURITY</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Terraform, Databricks, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c81be698ffb17b4e</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Software Engineer - Backend</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>COGENT SECURITY</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Terraform, Databricks, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d10b56d3761fa06a</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Adversarial Machine Learning Engineer - Red Teaming</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>C-Serv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, Hugging Face, TensorFlow, PyTorch, AKS, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=07b14e132a0081f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Adversarial Machine Learning Engineer - Red Teaming Contractor</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>C-Serv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, Hugging Face, TensorFlow, PyTorch, AKS, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1e7ca6a6c6ac2ee3</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Associate Cloud Engineer -</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Netsmart Technologies</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Overland Park, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f76cee0597823605</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-03.xlsx
+++ b/daily_matches/job_matches_2026-08-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Specialty Software Engineer</t>
+          <t>Data Scientist I and II (GCP &amp; AI Engineer)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>FedEx</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>25.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, BigQuery, FastAPI, Kubernetes, GitHub Actions, Terraform, Git, BigQuery</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, BigQuery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e1ab076bac74b1c</t>
+          <t>https://www.indeed.com/viewjob?jk=f01b4e79c2d80ad1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>24.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26738974b8469a72</t>
+          <t>https://www.indeed.com/viewjob?jk=add6ae06b73abbde</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Engineer II ( AI Platform)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>24.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, Docker, Kubernetes, CI/CD, Git</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ebcec5706e5970a</t>
+          <t>https://www.indeed.com/viewjob?jk=aff41faa0c819134</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Backend Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>24.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Kubernetes, Terraform, Git, PostgreSQL, MySQL, NoSQL, SQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8b19d5343bf31ae</t>
+          <t>https://www.indeed.com/viewjob?jk=25d2621640b91d6c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IPolarity LLC</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>24.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, AWS SageMaker, Azure ML, Kubernetes, CI/CD, Terraform, Git, Databricks, PySpark, Python</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5882bdc5a806f54</t>
+          <t>https://www.indeed.com/viewjob?jk=f9f9a9b29c45b0f5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>24.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, SQL, R</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a28196d6639ff9e7</t>
+          <t>https://www.indeed.com/viewjob?jk=d5db2f633e55af16</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>24.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Git, PostgreSQL, MySQL, Python, SQL, R, Java</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1f9392df8cc4ab5</t>
+          <t>https://www.indeed.com/viewjob?jk=2f50f278d449d2f7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Progressive Technology Solutions</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Oakbrook Terrace, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>24.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, AKS, CI/CD, Git, Kafka, SQL, R, Java</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c665fe23456b2833</t>
+          <t>https://www.indeed.com/viewjob?jk=b0fd03bd298d0bf4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AWS + AI-Native Developer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Senior Backend Developer</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>24.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Copilot, Pinecone, S3, EC2, MLflow, Git, Python</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a12625c776e70a7</t>
+          <t>https://www.indeed.com/viewjob?jk=6ce894b4a2950192</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cloud-Native Architect</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>24.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, Python, R, Java</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71f63292ca49d08f</t>
+          <t>https://www.indeed.com/viewjob?jk=5b83eef8d2024d1d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Autonomous Learning Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>24.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, Docker, Kubernetes, CI/CD, Python, R</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3fac1e6c2d2ae27</t>
+          <t>https://www.indeed.com/viewjob?jk=6c64a475c702ac68</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer, Palo Alto</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Rhombus Power</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>24.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, MySQL, MongoDB, NoSQL, Python, SQL, R, Java</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52e39436d6debc6</t>
+          <t>https://www.indeed.com/viewjob?jk=d128b733ad726488</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Engineer III - Software</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PODS</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>24.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Snowflake, PostgreSQL, SQL, R, Java</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d77313a791b9bf92</t>
+          <t>https://www.indeed.com/viewjob?jk=544f4ed8dc06503c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Hershey Company</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Hershey, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>24.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Databricks, PostgreSQL, MySQL, MongoDB, NoSQL, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21c0e185b38b0100</t>
+          <t>https://www.indeed.com/viewjob?jk=8c9451fdff0a56fe</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Westlake, TX</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>South Bend, IN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>24.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b75914a192898d1c</t>
+          <t>https://www.indeed.com/viewjob?jk=f3b818f1e20b1ad2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Jersey City, NJ</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>24.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09b326711b2a8ba0</t>
+          <t>https://www.indeed.com/viewjob?jk=a35bd74df1fa2c36</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Microsoft Azure Specialist</t>
+          <t>Operations Research Specialist - QuantumBlack Labs</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=797c8733d467365d</t>
+          <t>https://www.indeed.com/viewjob?jk=1986da97ab2e4bd0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Merrimack, NH</t>
+          <t>Operations Research Specialist - Critical Industries</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9e5552345b9c43f</t>
+          <t>https://www.indeed.com/viewjob?jk=787e122fda0f0eb5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer - Storage Infrastructure (Senior+)</t>
+          <t>AI Agentic Solutions Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>COGENT SECURITY</t>
+          <t>Confiz</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, S3, Athena, BigQuery, Terraform, Snowflake, Databricks, BigQuery, Kafka, Python</t>
+          <t>RAG, Prompt Engineering, Redshift, BigQuery, Docker, Kubernetes, CI/CD, Git, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd755b1e01cf4b25</t>
+          <t>https://www.indeed.com/viewjob?jk=2e667725f6fcbcd7</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer - Storage Infrastructure (Senior+)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>COGENT SECURITY</t>
+          <t>Warwick Investment Group</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, S3, Athena, BigQuery, Terraform, Snowflake, Databricks, BigQuery, Kafka, Python</t>
+          <t>Data Scientist, RAG, Copilot, Docker, CI/CD, Git, Snowflake, Kafka, Power BI, Python</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0249428e9fdabded</t>
+          <t>https://www.indeed.com/viewjob?jk=5e9fd3c8ca67917e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (C++, Parser /Compiler Development)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rocket Software</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Git, PostgreSQL, SQL, R, Java, C++, Scala</t>
+          <t>RAG, S3, MLflow, Kubernetes, Apache Airflow, Terraform, Kafka, Hadoop, Python, SQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=002ea5033c873dd5</t>
+          <t>https://www.indeed.com/viewjob?jk=b8353987748b8d8c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer, Content APIs</t>
+          <t>Software Engineer III - AI/ML Platform Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, MongoDB, Python, R, Java</t>
+          <t>Data Scientist, RAG, TensorFlow, Docker, Kubernetes, CI/CD, PostgreSQL, MongoDB, Cassandra, Python</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f1c8d538cec93de</t>
+          <t>https://www.indeed.com/viewjob?jk=9be9abf2ba504bc8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SOCOTEC Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R, Optimization</t>
+          <t>LangChain, RAG, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD, GitHub Actions, Git, Snowflake</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29dcdada1d61a998</t>
+          <t>https://www.indeed.com/viewjob?jk=d352556bfc9f8ca7</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Scientist - Atlanta, GA</t>
+          <t>Senior Data Engineer – Physical AI Platform, Data Engineering</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cortland</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Git, Databricks, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, S3, Kinesis, CI/CD, Jenkins, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c20e494fa3ce2a0</t>
+          <t>https://www.indeed.com/viewjob?jk=2ea0b33c2e692193</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer – Physical AI Platform, Data Engineering</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Rhombus Power</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, MySQL, SQL, R, Scala</t>
+          <t>RAG, S3, Kinesis, CI/CD, Jenkins, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec7f3e20ccb4fbba</t>
+          <t>https://www.indeed.com/viewjob?jk=c814a46cbb88f8ca</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Founding AI Engineer</t>
+          <t>Automation Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Greenberg Traurig</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, LLaMA, Copilot, Docker, Kubernetes, Python, R</t>
+          <t>LangChain, RAG, LLaMA, Prompt Engineering, FastAPI, Docker, Kubernetes, Python, R, Java</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a641f290ec2d05d7</t>
+          <t>https://www.indeed.com/viewjob?jk=d4ecbc5acd852e1f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AI - Process Engineering - Advisor II</t>
+          <t>Sr. Solutions Engineer - Digital Native Business, Named Accounts</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
+          <t>RAG, TensorFlow, PyTorch, MLflow, Git, Databricks, Kafka, Hadoop, Python, SQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8f99bab2bfd7689</t>
+          <t>https://www.indeed.com/viewjob?jk=2d5b0fb7d512fabd</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Threat Detection &amp; Automation Engineer</t>
+          <t>Sr. Solutions Engineer - Digital Native Business, FinTech</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, CI/CD, Terraform, Git, Python, SQL, R, Java</t>
+          <t>RAG, TensorFlow, PyTorch, MLflow, Git, Databricks, Kafka, Hadoop, Python, SQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21ba876d91e1bbc5</t>
+          <t>https://www.indeed.com/viewjob?jk=610c3a1bbde2965d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, AI Platform</t>
+          <t>Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (GCP)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EvenUp</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Kubernetes, Python, R, Java, Scala, Optimization</t>
+          <t>MLflow, Terraform, Databricks, Kafka, Hadoop, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=683cede4bf7b562b</t>
+          <t>https://www.indeed.com/viewjob?jk=6707e3755a595393</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Database and Applications Engineer</t>
+          <t>Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (Azure)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Adams and Reese LLP</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Git, Power BI, SQL, R, Java, Scala, Optimization</t>
+          <t>MLflow, Terraform, Databricks, Kafka, Hadoop, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=345f590a256aabe4</t>
+          <t>https://www.indeed.com/viewjob?jk=eadd2826582327ff</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>COGENT SECURITY</t>
+          <t>Excel Group</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Terraform, Databricks, Python, R, Scala, Optimization</t>
+          <t>RAG, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MySQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c81be698ffb17b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=896724692de28c2a</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend</t>
+          <t>Technology Internship Program - Summer 2027</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>COGENT SECURITY</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Terraform, Databricks, Python, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, Jenkins, Terraform, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d10b56d3761fa06a</t>
+          <t>https://www.indeed.com/viewjob?jk=7d7e5cde075b7a62</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Adversarial Machine Learning Engineer - Red Teaming</t>
+          <t>Software Engineering PMTS - Data Platform</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>C-Serv</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, Hugging Face, TensorFlow, PyTorch, AKS, Python, R, Optimization</t>
+          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Tableau, R, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07b14e132a0081f7</t>
+          <t>https://www.indeed.com/viewjob?jk=0650ba5d7effec70</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Adversarial Machine Learning Engineer - Red Teaming Contractor</t>
+          <t>Senior AI Cloud Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>C-Serv</t>
+          <t>Arizona State University</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, Hugging Face, TensorFlow, PyTorch, AKS, Python, R, Optimization</t>
+          <t>RAG, Prompt Engineering, S3, AKS, CI/CD, Terraform, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,42 +1651,322 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7ca6a6c6ac2ee3</t>
+          <t>https://www.indeed.com/viewjob?jk=db3049869dc54e81</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Associate Cloud Engineer -</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Netsmart Technologies</t>
+          <t>Dealer Tire</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, Prompt Engineering, Docker, Git, Snowflake, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=30cae7b45c5fa23a</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Associate Data Scientist</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Dealer Tire</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>OH, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, Prompt Engineering, Docker, Git, Snowflake, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eddef6349ebc5d13</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Software Engineer, Backend (C/C++)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>SpaceX</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Hawthorne, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, PostgreSQL, Python, SQL, R, Java, C++, Scala</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=537c2674ef2d50e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - Corporate Intelligence Platform</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Epsilon</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Copilot, Data Lake, Git, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8757e161bdfc3ca1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Analytics Data Engineer - Finance Decision Support</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Ferguson</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
         <v>10</v>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f76cee0597823605</t>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, Git, Databricks, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aca9c1591464e2f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Application Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Navy Federal Credit Union</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Vienna, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, CI/CD, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a10010ed5b4906ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Knowledge Graph Data Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>McKinsey &amp; Company</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Docker, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=08de86d7bec1a637</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>AI Engineer - Enterprise Business Systems</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Epsilon</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Git, Databricks, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c9b5743bc2d3703e</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Senior Systems Engineer II - Edge Platform &amp; Packaging (On-Prem)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Dispel</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Copilot, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e52a03d09803afc</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-03.xlsx
+++ b/daily_matches/job_matches_2026-08-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Scientist I and II (GCP &amp; AI Engineer)</t>
+          <t>Data Scientist / AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FedEx</t>
+          <t>LG Electronics</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25.6</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, BigQuery</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, BigQuery, FastAPI, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f01b4e79c2d80ad1</t>
+          <t>https://www.indeed.com/viewjob?jk=2503df5e5b9aa571</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>FalconSmartIT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>24.4</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone</t>
+          <t>AWS SageMaker, S3, Glue, Redshift, Kinesis, CI/CD, Snowflake, Databricks, Redshift, PySpark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=add6ae06b73abbde</t>
+          <t>https://www.indeed.com/viewjob?jk=c8c0d190ff6325ff</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Solutions Architect - Airflow - East Coast</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>24.4</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone</t>
+          <t>Redshift, BigQuery, Docker, Kubernetes, Apache Airflow, CI/CD, Snowflake, Databricks, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aff41faa0c819134</t>
+          <t>https://www.indeed.com/viewjob?jk=1a125f2d68a88fde</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Solutions Architect - Airflow - West Coast</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>24.4</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone</t>
+          <t>Redshift, BigQuery, Docker, Kubernetes, Apache Airflow, CI/CD, Snowflake, Databricks, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25d2621640b91d6c</t>
+          <t>https://www.indeed.com/viewjob?jk=310b444ca9a8968f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Full-Stack Developer - Integrations</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>24.4</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone</t>
+          <t>RAG, S3, Docker, AKS, CI/CD, Git, Databricks, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9f9a9b29c45b0f5</t>
+          <t>https://www.indeed.com/viewjob?jk=bcfbe0c6f553f175</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Generative AI / Enterprise Data Senior Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>General Dynamics Land Systems</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Sterling Heights, MI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>24.4</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone</t>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Synapse, Data Lake, CI/CD, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5db2f633e55af16</t>
+          <t>https://www.indeed.com/viewjob?jk=12938c2be38f82de</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Risk Data Scientist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>24.4</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone</t>
+          <t>Data Scientist, TensorFlow, PyTorch, Keras, Git, Kafka, Hadoop, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f50f278d449d2f7</t>
+          <t>https://www.indeed.com/viewjob?jk=17da3a6981410205</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Full-Stack Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Opiniion</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Oakbrook Terrace, IL, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>24.4</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone</t>
+          <t>RAG, S3, Docker, Git, PostgreSQL, MongoDB, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0fd03bd298d0bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=25a6de8b6b8c7098</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Software Engineer - Corporate GenAI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>24.4</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone</t>
+          <t>Generative AI, Prompt Engineering, CI/CD, Git, PostgreSQL, MySQL, MongoDB, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ce894b4a2950192</t>
+          <t>https://www.indeed.com/viewjob?jk=765f60c940d2cfd8</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Engineer III - Software</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>PODS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>24.4</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Snowflake, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b83eef8d2024d1d</t>
+          <t>https://www.indeed.com/viewjob?jk=c9ab5d1f7c807e52</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Nestlé USA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>24.4</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Azure ML, Snowflake, Databricks, Tableau, Power BI, Python, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c64a475c702ac68</t>
+          <t>https://www.indeed.com/viewjob?jk=5d68c1a7be48a080</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Azure Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Raritan, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>24.4</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone</t>
+          <t>RAG, S3, Glue, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d128b733ad726488</t>
+          <t>https://www.indeed.com/viewjob?jk=55b8b8abc753de7f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>LSEG (London Stock Exchange Group)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Liberty, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>24.4</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone</t>
+          <t>RAG, Snowflake, Kafka, PostgreSQL, MySQL, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=544f4ed8dc06503c</t>
+          <t>https://www.indeed.com/viewjob?jk=2208e782a315a688</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>NCR</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>24.4</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone</t>
+          <t>RAG, Copilot, Docker, Kubernetes, AKS, GitHub Actions, Git, SQL, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c9451fdff0a56fe</t>
+          <t>https://www.indeed.com/viewjob?jk=ad8e4afe6cf36792</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Sr. Data Scientist (Forecasting)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Nestlé USA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Bend, IN, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>24.4</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone</t>
+          <t>Data Scientist, RAG, Git, Snowflake, Databricks, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3b818f1e20b1ad2</t>
+          <t>https://www.indeed.com/viewjob?jk=afa70049b2cb6756</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Data Scientist - Digital Intelligence, Device Signals</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>24.4</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone</t>
+          <t>Data Scientist, RAG, TensorFlow, XGBoost, Git, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a35bd74df1fa2c36</t>
+          <t>https://www.indeed.com/viewjob?jk=ca9fc998857ec2aa</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Operations Research Specialist - QuantumBlack Labs</t>
+          <t>Senior Data Scientist - Digital Intelligence, Device Signals</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>18.9</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, PySpark</t>
+          <t>Data Scientist, RAG, TensorFlow, XGBoost, Git, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1986da97ab2e4bd0</t>
+          <t>https://www.indeed.com/viewjob?jk=b94723d761d3be07</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Operations Research Specialist - Critical Industries</t>
+          <t>Senior Data Scientist - Digital Intelligence, Device Signals</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>18.9</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Docker, Kubernetes, CI/CD, Git, Databricks, PySpark</t>
+          <t>Data Scientist, RAG, TensorFlow, XGBoost, Git, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=787e122fda0f0eb5</t>
+          <t>https://www.indeed.com/viewjob?jk=982bc98d57a476e7</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Agentic Solutions Engineer</t>
+          <t>AI SaaS Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Confiz</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16.7</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Redshift, BigQuery, Docker, Kubernetes, CI/CD, Git, BigQuery, Redshift</t>
+          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e667725f6fcbcd7</t>
+          <t>https://www.indeed.com/viewjob?jk=e5ba546b5e5bd8d0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Developer Advocate</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Warwick Investment Group</t>
+          <t>Teradata</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Docker, CI/CD, Git, Snowflake, Kafka, Power BI, Python</t>
+          <t>Data Scientist, LangChain, RAG, Copilot, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,67 +1161,67 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e9fd3c8ca67917e</t>
+          <t>https://www.indeed.com/viewjob?jk=fad48e8d50a11ac3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Talkspace</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, S3, MLflow, Kubernetes, Apache Airflow, Terraform, Kafka, Hadoop, Python, SQL</t>
+          <t>AI Engineer, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8353987748b8d8c</t>
+          <t>https://www.indeed.com/viewjob?jk=0eef98faac736b11</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, Docker, Kubernetes, CI/CD, PostgreSQL, MongoDB, Cassandra, Python</t>
+          <t>Data Scientist, RAG, Databricks, PySpark, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be9abf2ba504bc8</t>
+          <t>https://www.indeed.com/viewjob?jk=dba3c28dff2c2665</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SOCOTEC Group</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD, GitHub Actions, Git, Snowflake</t>
+          <t>Data Scientist, RAG, Databricks, PySpark, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d352556bfc9f8ca7</t>
+          <t>https://www.indeed.com/viewjob?jk=f23005bc37f3f527</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Physical AI Platform, Data Engineering</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Consumers Energy</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, S3, Kinesis, CI/CD, Jenkins, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Data Lake, Databricks, PySpark, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ea0b33c2e692193</t>
+          <t>https://www.indeed.com/viewjob?jk=100d36e57f68f74b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Physical AI Platform, Data Engineering</t>
+          <t>LLM DevOps/Inference Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>iTemp</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, S3, Kinesis, CI/CD, Jenkins, Git, NoSQL, Python, SQL, R</t>
+          <t>AI Engineer, Gemini, AWS SageMaker, EC2, CI/CD, Terraform, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c814a46cbb88f8ca</t>
+          <t>https://www.indeed.com/viewjob?jk=115c5a51491fb7bd</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Automation Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Greenberg Traurig</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Prompt Engineering, FastAPI, Docker, Kubernetes, Python, R, Java</t>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4ecbc5acd852e1f</t>
+          <t>https://www.indeed.com/viewjob?jk=bcccf48bb0411667</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer - Digital Native Business, Named Accounts</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Raritan, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, MLflow, Git, Databricks, Kafka, Hadoop, Python, SQL</t>
+          <t>RAG, Data Lake, Databricks, PySpark, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d5b0fb7d512fabd</t>
+          <t>https://www.indeed.com/viewjob?jk=e670572ccedcb37d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer - Digital Native Business, FinTech</t>
+          <t>Junior AI Programmer-NO remote-Las Vegas ONLY</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Office Equipment Company</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, MLflow, Git, Databricks, Kafka, Hadoop, Python, SQL</t>
+          <t>RAG, Copilot, Git, PostgreSQL, Tableau, Power BI, SQL, R, Java</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=610c3a1bbde2965d</t>
+          <t>https://www.indeed.com/viewjob?jk=e9a8c9242b6c7917</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (GCP)</t>
+          <t>AI ENGINEER</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>MGI,inc.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>MLflow, Terraform, Databricks, Kafka, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, RAG, LLaMA, TensorFlow, Hadoop, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6707e3755a595393</t>
+          <t>https://www.indeed.com/viewjob?jk=b0933528f241443b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (Azure)</t>
+          <t>Healthcare Data Scientist</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Cherokee Federal</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>MLflow, Terraform, Databricks, Kafka, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Synapse, Git, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eadd2826582327ff</t>
+          <t>https://www.indeed.com/viewjob?jk=f46a6a98a325f97d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Engineer_Data Engineer_7</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Excel Group</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MySQL, SQL, R, Scala</t>
+          <t>RAG, BigQuery, CI/CD, Git, BigQuery, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=896724692de28c2a</t>
+          <t>https://www.indeed.com/viewjob?jk=5907802ebef017e2</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Technology Internship Program - Summer 2027</t>
+          <t>Data Scientist and AI Specialist</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>NexOne, Inc.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Clearfield, UT, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Jenkins, Terraform, NoSQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Pinecone, Python, R, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,392 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d7e5cde075b7a62</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Software Engineering PMTS - Data Platform</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Salesforce</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Tableau, R, Scala</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0650ba5d7effec70</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Senior AI Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Arizona State University</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Scottsdale, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, S3, AKS, CI/CD, Terraform, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=db3049869dc54e81</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Associate Data Scientist</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Dealer Tire</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Cleveland, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, RAG, Prompt Engineering, Docker, Git, Snowflake, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=30cae7b45c5fa23a</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Associate Data Scientist</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Dealer Tire</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>OH, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, RAG, Prompt Engineering, Docker, Git, Snowflake, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eddef6349ebc5d13</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Software Engineer, Backend (C/C++)</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>SpaceX</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Hawthorne, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, PostgreSQL, Python, SQL, R, Java, C++, Scala</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=537c2674ef2d50e0</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer - Corporate Intelligence Platform</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Epsilon</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Copilot, Data Lake, Git, Databricks, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8757e161bdfc3ca1</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Analytics Data Engineer - Finance Decision Support</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Ferguson</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>10</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>RAG, Git, Databricks, Power BI, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aca9c1591464e2f8</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Application Engineer</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Navy Federal Credit Union</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Vienna, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>10</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, CI/CD, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a10010ed5b4906ec</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Knowledge Graph Data Engineer</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>McKinsey &amp; Company</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>10</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Docker, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=08de86d7bec1a637</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>AI Engineer - Enterprise Business Systems</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Epsilon</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>10</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Git, Databricks, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c9b5743bc2d3703e</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Senior Systems Engineer II - Edge Platform &amp; Packaging (On-Prem)</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Dispel</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>10</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Copilot, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e52a03d09803afc</t>
+          <t>https://www.indeed.com/viewjob?jk=13072dc55188e3bf</t>
         </is>
       </c>
     </row>
